--- a/crisscross_kit/crisscross/dna_source_plates/assembly_plates/P3660_MA_H2_antihandles_S2C.xlsx
+++ b/crisscross_kit/crisscross/dna_source_plates/assembly_plates/P3660_MA_H2_antihandles_S2C.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matt/Documents/Shih_Lab_Postdoc/research_projects/crisscross_code/crisscross_kit/crisscross/dna_source_plates/assembly_plates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4145466-F82A-C94A-B799-37227FCA5FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="25600" yWindow="620" windowWidth="25600" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Data" sheetId="1" r:id="rId1"/>
     <sheet name="2D Layout" sheetId="2" r:id="rId2"/>
     <sheet name="2D Label" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1198">
   <si>
     <t>well</t>
   </si>
@@ -3615,8 +3621,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3693,13 +3699,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3737,7 +3751,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3771,6 +3785,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3805,9 +3820,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3980,18 +3996,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E385"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="42.7109375" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" customWidth="1"/>
-    <col min="4" max="4" width="70.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" customWidth="1"/>
+    <col min="4" max="4" width="70.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4008,7 +4024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -4022,10 +4038,10 @@
         <v>901</v>
       </c>
       <c r="E2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4039,10 +4055,10 @@
         <v>902</v>
       </c>
       <c r="E3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4056,10 +4072,10 @@
         <v>903</v>
       </c>
       <c r="E4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4073,10 +4089,10 @@
         <v>904</v>
       </c>
       <c r="E5">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4090,10 +4106,10 @@
         <v>905</v>
       </c>
       <c r="E6">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4107,10 +4123,10 @@
         <v>906</v>
       </c>
       <c r="E7">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -4124,10 +4140,10 @@
         <v>907</v>
       </c>
       <c r="E8">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4141,10 +4157,10 @@
         <v>908</v>
       </c>
       <c r="E9">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -4158,10 +4174,10 @@
         <v>909</v>
       </c>
       <c r="E10">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -4175,10 +4191,10 @@
         <v>910</v>
       </c>
       <c r="E11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -4192,10 +4208,10 @@
         <v>911</v>
       </c>
       <c r="E12">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4209,10 +4225,10 @@
         <v>912</v>
       </c>
       <c r="E13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -4226,10 +4242,10 @@
         <v>913</v>
       </c>
       <c r="E14">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4243,10 +4259,10 @@
         <v>914</v>
       </c>
       <c r="E15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -4260,10 +4276,10 @@
         <v>915</v>
       </c>
       <c r="E16">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -4277,10 +4293,10 @@
         <v>916</v>
       </c>
       <c r="E17">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -4294,10 +4310,10 @@
         <v>917</v>
       </c>
       <c r="E18">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -4311,10 +4327,10 @@
         <v>918</v>
       </c>
       <c r="E19">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4328,10 +4344,10 @@
         <v>919</v>
       </c>
       <c r="E20">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4345,10 +4361,10 @@
         <v>920</v>
       </c>
       <c r="E21">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -4362,10 +4378,10 @@
         <v>921</v>
       </c>
       <c r="E22">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4379,10 +4395,10 @@
         <v>922</v>
       </c>
       <c r="E23">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -4396,10 +4412,10 @@
         <v>923</v>
       </c>
       <c r="E24">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -4413,10 +4429,10 @@
         <v>924</v>
       </c>
       <c r="E25">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -4430,10 +4446,10 @@
         <v>925</v>
       </c>
       <c r="E26">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -4447,10 +4463,10 @@
         <v>926</v>
       </c>
       <c r="E27">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -4464,10 +4480,10 @@
         <v>927</v>
       </c>
       <c r="E28">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -4481,10 +4497,10 @@
         <v>928</v>
       </c>
       <c r="E29">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -4498,10 +4514,10 @@
         <v>929</v>
       </c>
       <c r="E30">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -4515,10 +4531,10 @@
         <v>930</v>
       </c>
       <c r="E31">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -4532,10 +4548,10 @@
         <v>931</v>
       </c>
       <c r="E32">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -4549,10 +4565,10 @@
         <v>932</v>
       </c>
       <c r="E33">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -4566,10 +4582,10 @@
         <v>933</v>
       </c>
       <c r="E34">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -4583,10 +4599,10 @@
         <v>934</v>
       </c>
       <c r="E35">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -4600,10 +4616,10 @@
         <v>935</v>
       </c>
       <c r="E36">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -4617,10 +4633,10 @@
         <v>936</v>
       </c>
       <c r="E37">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -4634,10 +4650,10 @@
         <v>937</v>
       </c>
       <c r="E38">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -4651,10 +4667,10 @@
         <v>938</v>
       </c>
       <c r="E39">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -4668,10 +4684,10 @@
         <v>939</v>
       </c>
       <c r="E40">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -4685,10 +4701,10 @@
         <v>940</v>
       </c>
       <c r="E41">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4702,10 +4718,10 @@
         <v>941</v>
       </c>
       <c r="E42">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -4719,10 +4735,10 @@
         <v>942</v>
       </c>
       <c r="E43">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -4736,10 +4752,10 @@
         <v>943</v>
       </c>
       <c r="E44">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -4753,10 +4769,10 @@
         <v>944</v>
       </c>
       <c r="E45">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -4770,10 +4786,10 @@
         <v>945</v>
       </c>
       <c r="E46">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -4787,10 +4803,10 @@
         <v>946</v>
       </c>
       <c r="E47">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -4804,10 +4820,10 @@
         <v>947</v>
       </c>
       <c r="E48">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -4821,10 +4837,10 @@
         <v>948</v>
       </c>
       <c r="E49">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -4838,10 +4854,10 @@
         <v>949</v>
       </c>
       <c r="E50">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -4855,10 +4871,10 @@
         <v>950</v>
       </c>
       <c r="E51">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -4872,10 +4888,10 @@
         <v>951</v>
       </c>
       <c r="E52">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -4889,10 +4905,10 @@
         <v>952</v>
       </c>
       <c r="E53">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -4906,10 +4922,10 @@
         <v>953</v>
       </c>
       <c r="E54">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -4923,10 +4939,10 @@
         <v>954</v>
       </c>
       <c r="E55">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -4940,10 +4956,10 @@
         <v>955</v>
       </c>
       <c r="E56">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -4957,10 +4973,10 @@
         <v>956</v>
       </c>
       <c r="E57">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -4974,10 +4990,10 @@
         <v>957</v>
       </c>
       <c r="E58">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -4991,10 +5007,10 @@
         <v>958</v>
       </c>
       <c r="E59">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -5008,10 +5024,10 @@
         <v>959</v>
       </c>
       <c r="E60">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -5025,10 +5041,10 @@
         <v>960</v>
       </c>
       <c r="E61">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -5042,10 +5058,10 @@
         <v>961</v>
       </c>
       <c r="E62">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -5059,10 +5075,10 @@
         <v>962</v>
       </c>
       <c r="E63">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -5076,10 +5092,10 @@
         <v>963</v>
       </c>
       <c r="E64">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -5093,10 +5109,10 @@
         <v>964</v>
       </c>
       <c r="E65">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -5110,10 +5126,10 @@
         <v>965</v>
       </c>
       <c r="E66">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -5127,10 +5143,10 @@
         <v>966</v>
       </c>
       <c r="E67">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -5144,10 +5160,10 @@
         <v>967</v>
       </c>
       <c r="E68">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -5161,10 +5177,10 @@
         <v>968</v>
       </c>
       <c r="E69">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -5178,10 +5194,10 @@
         <v>969</v>
       </c>
       <c r="E70">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -5195,10 +5211,10 @@
         <v>970</v>
       </c>
       <c r="E71">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -5212,10 +5228,10 @@
         <v>971</v>
       </c>
       <c r="E72">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -5229,10 +5245,10 @@
         <v>972</v>
       </c>
       <c r="E73">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -5246,10 +5262,10 @@
         <v>973</v>
       </c>
       <c r="E74">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -5263,10 +5279,10 @@
         <v>974</v>
       </c>
       <c r="E75">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -5280,10 +5296,10 @@
         <v>975</v>
       </c>
       <c r="E76">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -5297,10 +5313,10 @@
         <v>976</v>
       </c>
       <c r="E77">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -5314,10 +5330,10 @@
         <v>977</v>
       </c>
       <c r="E78">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -5331,10 +5347,10 @@
         <v>978</v>
       </c>
       <c r="E79">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -5348,10 +5364,10 @@
         <v>979</v>
       </c>
       <c r="E80">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -5365,10 +5381,10 @@
         <v>980</v>
       </c>
       <c r="E81">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -5382,10 +5398,10 @@
         <v>981</v>
       </c>
       <c r="E82">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -5399,10 +5415,10 @@
         <v>982</v>
       </c>
       <c r="E83">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -5416,10 +5432,10 @@
         <v>983</v>
       </c>
       <c r="E84">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -5433,10 +5449,10 @@
         <v>984</v>
       </c>
       <c r="E85">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -5450,10 +5466,10 @@
         <v>985</v>
       </c>
       <c r="E86">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -5467,10 +5483,10 @@
         <v>986</v>
       </c>
       <c r="E87">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -5484,10 +5500,10 @@
         <v>987</v>
       </c>
       <c r="E88">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -5501,10 +5517,10 @@
         <v>988</v>
       </c>
       <c r="E89">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -5518,10 +5534,10 @@
         <v>989</v>
       </c>
       <c r="E90">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -5535,10 +5551,10 @@
         <v>990</v>
       </c>
       <c r="E91">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -5552,10 +5568,10 @@
         <v>991</v>
       </c>
       <c r="E92">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -5569,10 +5585,10 @@
         <v>992</v>
       </c>
       <c r="E93">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -5586,10 +5602,10 @@
         <v>993</v>
       </c>
       <c r="E94">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -5603,10 +5619,10 @@
         <v>994</v>
       </c>
       <c r="E95">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -5620,10 +5636,10 @@
         <v>995</v>
       </c>
       <c r="E96">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -5637,10 +5653,10 @@
         <v>996</v>
       </c>
       <c r="E97">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -5654,10 +5670,10 @@
         <v>997</v>
       </c>
       <c r="E98">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -5671,10 +5687,10 @@
         <v>998</v>
       </c>
       <c r="E99">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>103</v>
       </c>
@@ -5688,10 +5704,10 @@
         <v>999</v>
       </c>
       <c r="E100">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>104</v>
       </c>
@@ -5705,10 +5721,10 @@
         <v>1000</v>
       </c>
       <c r="E101">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>105</v>
       </c>
@@ -5722,10 +5738,10 @@
         <v>1001</v>
       </c>
       <c r="E102">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>106</v>
       </c>
@@ -5739,10 +5755,10 @@
         <v>1002</v>
       </c>
       <c r="E103">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>107</v>
       </c>
@@ -5756,10 +5772,10 @@
         <v>1003</v>
       </c>
       <c r="E104">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>108</v>
       </c>
@@ -5773,10 +5789,10 @@
         <v>1004</v>
       </c>
       <c r="E105">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>109</v>
       </c>
@@ -5790,10 +5806,10 @@
         <v>1005</v>
       </c>
       <c r="E106">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>110</v>
       </c>
@@ -5807,10 +5823,10 @@
         <v>1006</v>
       </c>
       <c r="E107">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>111</v>
       </c>
@@ -5824,10 +5840,10 @@
         <v>1007</v>
       </c>
       <c r="E108">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>112</v>
       </c>
@@ -5841,10 +5857,10 @@
         <v>1008</v>
       </c>
       <c r="E109">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>113</v>
       </c>
@@ -5858,10 +5874,10 @@
         <v>1009</v>
       </c>
       <c r="E110">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>114</v>
       </c>
@@ -5875,10 +5891,10 @@
         <v>1010</v>
       </c>
       <c r="E111">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>115</v>
       </c>
@@ -5892,10 +5908,10 @@
         <v>1011</v>
       </c>
       <c r="E112">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>116</v>
       </c>
@@ -5909,10 +5925,10 @@
         <v>1012</v>
       </c>
       <c r="E113">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>117</v>
       </c>
@@ -5926,10 +5942,10 @@
         <v>1013</v>
       </c>
       <c r="E114">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>118</v>
       </c>
@@ -5943,10 +5959,10 @@
         <v>1014</v>
       </c>
       <c r="E115">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>119</v>
       </c>
@@ -5960,10 +5976,10 @@
         <v>1015</v>
       </c>
       <c r="E116">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>120</v>
       </c>
@@ -5977,10 +5993,10 @@
         <v>1016</v>
       </c>
       <c r="E117">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -5994,10 +6010,10 @@
         <v>1017</v>
       </c>
       <c r="E118">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>122</v>
       </c>
@@ -6011,10 +6027,10 @@
         <v>1018</v>
       </c>
       <c r="E119">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>123</v>
       </c>
@@ -6028,10 +6044,10 @@
         <v>1019</v>
       </c>
       <c r="E120">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>124</v>
       </c>
@@ -6045,10 +6061,10 @@
         <v>1020</v>
       </c>
       <c r="E121">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>125</v>
       </c>
@@ -6062,10 +6078,10 @@
         <v>1021</v>
       </c>
       <c r="E122">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>126</v>
       </c>
@@ -6079,10 +6095,10 @@
         <v>1022</v>
       </c>
       <c r="E123">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>127</v>
       </c>
@@ -6096,10 +6112,10 @@
         <v>1023</v>
       </c>
       <c r="E124">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>128</v>
       </c>
@@ -6113,10 +6129,10 @@
         <v>1024</v>
       </c>
       <c r="E125">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>129</v>
       </c>
@@ -6130,10 +6146,10 @@
         <v>1025</v>
       </c>
       <c r="E126">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>130</v>
       </c>
@@ -6147,10 +6163,10 @@
         <v>1026</v>
       </c>
       <c r="E127">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>131</v>
       </c>
@@ -6164,10 +6180,10 @@
         <v>1027</v>
       </c>
       <c r="E128">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>132</v>
       </c>
@@ -6181,10 +6197,10 @@
         <v>1028</v>
       </c>
       <c r="E129">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>133</v>
       </c>
@@ -6198,10 +6214,10 @@
         <v>1029</v>
       </c>
       <c r="E130">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>134</v>
       </c>
@@ -6215,10 +6231,10 @@
         <v>1030</v>
       </c>
       <c r="E131">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>135</v>
       </c>
@@ -6232,10 +6248,10 @@
         <v>1031</v>
       </c>
       <c r="E132">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>136</v>
       </c>
@@ -6249,10 +6265,10 @@
         <v>1032</v>
       </c>
       <c r="E133">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>137</v>
       </c>
@@ -6266,10 +6282,10 @@
         <v>1033</v>
       </c>
       <c r="E134">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>138</v>
       </c>
@@ -6283,10 +6299,10 @@
         <v>1034</v>
       </c>
       <c r="E135">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -6300,10 +6316,10 @@
         <v>1035</v>
       </c>
       <c r="E136">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -6317,10 +6333,10 @@
         <v>1036</v>
       </c>
       <c r="E137">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>141</v>
       </c>
@@ -6334,10 +6350,10 @@
         <v>1037</v>
       </c>
       <c r="E138">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>142</v>
       </c>
@@ -6351,10 +6367,10 @@
         <v>1038</v>
       </c>
       <c r="E139">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>143</v>
       </c>
@@ -6368,10 +6384,10 @@
         <v>1039</v>
       </c>
       <c r="E140">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>144</v>
       </c>
@@ -6385,10 +6401,10 @@
         <v>1040</v>
       </c>
       <c r="E141">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>145</v>
       </c>
@@ -6402,10 +6418,10 @@
         <v>1041</v>
       </c>
       <c r="E142">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>146</v>
       </c>
@@ -6419,10 +6435,10 @@
         <v>1042</v>
       </c>
       <c r="E143">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -6436,10 +6452,10 @@
         <v>1043</v>
       </c>
       <c r="E144">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>148</v>
       </c>
@@ -6453,10 +6469,10 @@
         <v>1044</v>
       </c>
       <c r="E145">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>149</v>
       </c>
@@ -6470,10 +6486,10 @@
         <v>1045</v>
       </c>
       <c r="E146">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>150</v>
       </c>
@@ -6487,10 +6503,10 @@
         <v>1046</v>
       </c>
       <c r="E147">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>151</v>
       </c>
@@ -6504,10 +6520,10 @@
         <v>1047</v>
       </c>
       <c r="E148">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>152</v>
       </c>
@@ -6521,10 +6537,10 @@
         <v>1048</v>
       </c>
       <c r="E149">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>153</v>
       </c>
@@ -6538,10 +6554,10 @@
         <v>1049</v>
       </c>
       <c r="E150">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>154</v>
       </c>
@@ -6555,10 +6571,10 @@
         <v>1050</v>
       </c>
       <c r="E151">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>155</v>
       </c>
@@ -6572,10 +6588,10 @@
         <v>1051</v>
       </c>
       <c r="E152">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>156</v>
       </c>
@@ -6589,10 +6605,10 @@
         <v>1052</v>
       </c>
       <c r="E153">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>157</v>
       </c>
@@ -6606,10 +6622,10 @@
         <v>1053</v>
       </c>
       <c r="E154">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>158</v>
       </c>
@@ -6623,10 +6639,10 @@
         <v>1054</v>
       </c>
       <c r="E155">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>159</v>
       </c>
@@ -6640,10 +6656,10 @@
         <v>1055</v>
       </c>
       <c r="E156">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>160</v>
       </c>
@@ -6657,10 +6673,10 @@
         <v>1056</v>
       </c>
       <c r="E157">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>161</v>
       </c>
@@ -6674,10 +6690,10 @@
         <v>1057</v>
       </c>
       <c r="E158">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>162</v>
       </c>
@@ -6691,10 +6707,10 @@
         <v>1058</v>
       </c>
       <c r="E159">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>163</v>
       </c>
@@ -6708,10 +6724,10 @@
         <v>1059</v>
       </c>
       <c r="E160">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>164</v>
       </c>
@@ -6725,10 +6741,10 @@
         <v>1060</v>
       </c>
       <c r="E161">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>165</v>
       </c>
@@ -6742,10 +6758,10 @@
         <v>1061</v>
       </c>
       <c r="E162">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -6759,10 +6775,10 @@
         <v>1062</v>
       </c>
       <c r="E163">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>167</v>
       </c>
@@ -6776,10 +6792,10 @@
         <v>1063</v>
       </c>
       <c r="E164">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -6793,10 +6809,10 @@
         <v>1064</v>
       </c>
       <c r="E165">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>169</v>
       </c>
@@ -6810,10 +6826,10 @@
         <v>1065</v>
       </c>
       <c r="E166">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -6827,10 +6843,10 @@
         <v>1066</v>
       </c>
       <c r="E167">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>171</v>
       </c>
@@ -6844,10 +6860,10 @@
         <v>1067</v>
       </c>
       <c r="E168">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>172</v>
       </c>
@@ -6861,10 +6877,10 @@
         <v>1068</v>
       </c>
       <c r="E169">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>173</v>
       </c>
@@ -6878,10 +6894,10 @@
         <v>1069</v>
       </c>
       <c r="E170">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>174</v>
       </c>
@@ -6895,10 +6911,10 @@
         <v>1070</v>
       </c>
       <c r="E171">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>175</v>
       </c>
@@ -6912,10 +6928,10 @@
         <v>1071</v>
       </c>
       <c r="E172">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>176</v>
       </c>
@@ -6929,10 +6945,10 @@
         <v>1072</v>
       </c>
       <c r="E173">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>177</v>
       </c>
@@ -6946,10 +6962,10 @@
         <v>1073</v>
       </c>
       <c r="E174">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>178</v>
       </c>
@@ -6963,10 +6979,10 @@
         <v>1074</v>
       </c>
       <c r="E175">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>179</v>
       </c>
@@ -6980,10 +6996,10 @@
         <v>1075</v>
       </c>
       <c r="E176">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>180</v>
       </c>
@@ -6997,10 +7013,10 @@
         <v>1076</v>
       </c>
       <c r="E177">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>181</v>
       </c>
@@ -7014,10 +7030,10 @@
         <v>1077</v>
       </c>
       <c r="E178">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>182</v>
       </c>
@@ -7031,10 +7047,10 @@
         <v>1078</v>
       </c>
       <c r="E179">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>183</v>
       </c>
@@ -7048,10 +7064,10 @@
         <v>1079</v>
       </c>
       <c r="E180">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>184</v>
       </c>
@@ -7065,10 +7081,10 @@
         <v>1080</v>
       </c>
       <c r="E181">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>185</v>
       </c>
@@ -7082,10 +7098,10 @@
         <v>1081</v>
       </c>
       <c r="E182">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>186</v>
       </c>
@@ -7099,10 +7115,10 @@
         <v>1082</v>
       </c>
       <c r="E183">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>187</v>
       </c>
@@ -7116,10 +7132,10 @@
         <v>1083</v>
       </c>
       <c r="E184">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>188</v>
       </c>
@@ -7133,10 +7149,10 @@
         <v>1084</v>
       </c>
       <c r="E185">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>189</v>
       </c>
@@ -7150,10 +7166,10 @@
         <v>1085</v>
       </c>
       <c r="E186">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>190</v>
       </c>
@@ -7167,10 +7183,10 @@
         <v>1086</v>
       </c>
       <c r="E187">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>191</v>
       </c>
@@ -7184,10 +7200,10 @@
         <v>1087</v>
       </c>
       <c r="E188">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>192</v>
       </c>
@@ -7201,10 +7217,10 @@
         <v>1088</v>
       </c>
       <c r="E189">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>193</v>
       </c>
@@ -7218,10 +7234,10 @@
         <v>1089</v>
       </c>
       <c r="E190">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>194</v>
       </c>
@@ -7235,10 +7251,10 @@
         <v>1090</v>
       </c>
       <c r="E191">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>195</v>
       </c>
@@ -7252,10 +7268,10 @@
         <v>1091</v>
       </c>
       <c r="E192">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>196</v>
       </c>
@@ -7269,10 +7285,10 @@
         <v>1092</v>
       </c>
       <c r="E193">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>197</v>
       </c>
@@ -7286,10 +7302,10 @@
         <v>1093</v>
       </c>
       <c r="E194">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>198</v>
       </c>
@@ -7303,10 +7319,10 @@
         <v>1094</v>
       </c>
       <c r="E195">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -7320,10 +7336,10 @@
         <v>1095</v>
       </c>
       <c r="E196">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>200</v>
       </c>
@@ -7337,10 +7353,10 @@
         <v>1096</v>
       </c>
       <c r="E197">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>201</v>
       </c>
@@ -7354,10 +7370,10 @@
         <v>1097</v>
       </c>
       <c r="E198">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>202</v>
       </c>
@@ -7371,10 +7387,10 @@
         <v>1098</v>
       </c>
       <c r="E199">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>203</v>
       </c>
@@ -7388,10 +7404,10 @@
         <v>1099</v>
       </c>
       <c r="E200">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>204</v>
       </c>
@@ -7405,10 +7421,10 @@
         <v>1100</v>
       </c>
       <c r="E201">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>205</v>
       </c>
@@ -7422,10 +7438,10 @@
         <v>1101</v>
       </c>
       <c r="E202">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>206</v>
       </c>
@@ -7439,10 +7455,10 @@
         <v>1102</v>
       </c>
       <c r="E203">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>207</v>
       </c>
@@ -7456,10 +7472,10 @@
         <v>1103</v>
       </c>
       <c r="E204">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>208</v>
       </c>
@@ -7473,10 +7489,10 @@
         <v>1104</v>
       </c>
       <c r="E205">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>209</v>
       </c>
@@ -7490,10 +7506,10 @@
         <v>1105</v>
       </c>
       <c r="E206">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>210</v>
       </c>
@@ -7507,10 +7523,10 @@
         <v>1106</v>
       </c>
       <c r="E207">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>211</v>
       </c>
@@ -7524,10 +7540,10 @@
         <v>1107</v>
       </c>
       <c r="E208">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>212</v>
       </c>
@@ -7541,10 +7557,10 @@
         <v>1108</v>
       </c>
       <c r="E209">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>213</v>
       </c>
@@ -7558,10 +7574,10 @@
         <v>1109</v>
       </c>
       <c r="E210">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>214</v>
       </c>
@@ -7575,10 +7591,10 @@
         <v>1110</v>
       </c>
       <c r="E211">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>215</v>
       </c>
@@ -7592,10 +7608,10 @@
         <v>1111</v>
       </c>
       <c r="E212">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>216</v>
       </c>
@@ -7609,10 +7625,10 @@
         <v>1112</v>
       </c>
       <c r="E213">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>217</v>
       </c>
@@ -7626,10 +7642,10 @@
         <v>1113</v>
       </c>
       <c r="E214">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>218</v>
       </c>
@@ -7643,10 +7659,10 @@
         <v>1114</v>
       </c>
       <c r="E215">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>219</v>
       </c>
@@ -7660,10 +7676,10 @@
         <v>1115</v>
       </c>
       <c r="E216">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>220</v>
       </c>
@@ -7677,10 +7693,10 @@
         <v>1116</v>
       </c>
       <c r="E217">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>221</v>
       </c>
@@ -7694,10 +7710,10 @@
         <v>1117</v>
       </c>
       <c r="E218">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>222</v>
       </c>
@@ -7711,10 +7727,10 @@
         <v>1118</v>
       </c>
       <c r="E219">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>223</v>
       </c>
@@ -7728,10 +7744,10 @@
         <v>1119</v>
       </c>
       <c r="E220">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>224</v>
       </c>
@@ -7745,10 +7761,10 @@
         <v>1120</v>
       </c>
       <c r="E221">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>225</v>
       </c>
@@ -7762,10 +7778,10 @@
         <v>1121</v>
       </c>
       <c r="E222">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>226</v>
       </c>
@@ -7779,10 +7795,10 @@
         <v>1122</v>
       </c>
       <c r="E223">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>227</v>
       </c>
@@ -7796,10 +7812,10 @@
         <v>1123</v>
       </c>
       <c r="E224">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>228</v>
       </c>
@@ -7813,10 +7829,10 @@
         <v>1124</v>
       </c>
       <c r="E225">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>229</v>
       </c>
@@ -7830,10 +7846,10 @@
         <v>1125</v>
       </c>
       <c r="E226">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>230</v>
       </c>
@@ -7847,10 +7863,10 @@
         <v>1126</v>
       </c>
       <c r="E227">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>231</v>
       </c>
@@ -7864,10 +7880,10 @@
         <v>1127</v>
       </c>
       <c r="E228">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>232</v>
       </c>
@@ -7881,10 +7897,10 @@
         <v>1128</v>
       </c>
       <c r="E229">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>233</v>
       </c>
@@ -7898,10 +7914,10 @@
         <v>1129</v>
       </c>
       <c r="E230">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>234</v>
       </c>
@@ -7915,10 +7931,10 @@
         <v>1130</v>
       </c>
       <c r="E231">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>235</v>
       </c>
@@ -7932,10 +7948,10 @@
         <v>1131</v>
       </c>
       <c r="E232">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>236</v>
       </c>
@@ -7949,10 +7965,10 @@
         <v>1132</v>
       </c>
       <c r="E233">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>237</v>
       </c>
@@ -7966,10 +7982,10 @@
         <v>1133</v>
       </c>
       <c r="E234">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>238</v>
       </c>
@@ -7983,10 +7999,10 @@
         <v>1134</v>
       </c>
       <c r="E235">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>239</v>
       </c>
@@ -8000,10 +8016,10 @@
         <v>1135</v>
       </c>
       <c r="E236">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>240</v>
       </c>
@@ -8017,10 +8033,10 @@
         <v>1136</v>
       </c>
       <c r="E237">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>241</v>
       </c>
@@ -8034,10 +8050,10 @@
         <v>1137</v>
       </c>
       <c r="E238">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>242</v>
       </c>
@@ -8051,10 +8067,10 @@
         <v>1138</v>
       </c>
       <c r="E239">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>243</v>
       </c>
@@ -8068,10 +8084,10 @@
         <v>1139</v>
       </c>
       <c r="E240">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>244</v>
       </c>
@@ -8085,10 +8101,10 @@
         <v>1140</v>
       </c>
       <c r="E241">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>245</v>
       </c>
@@ -8102,10 +8118,10 @@
         <v>1141</v>
       </c>
       <c r="E242">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>246</v>
       </c>
@@ -8119,10 +8135,10 @@
         <v>1142</v>
       </c>
       <c r="E243">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>247</v>
       </c>
@@ -8136,10 +8152,10 @@
         <v>1143</v>
       </c>
       <c r="E244">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>248</v>
       </c>
@@ -8153,10 +8169,10 @@
         <v>1144</v>
       </c>
       <c r="E245">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>249</v>
       </c>
@@ -8170,10 +8186,10 @@
         <v>1145</v>
       </c>
       <c r="E246">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>250</v>
       </c>
@@ -8187,10 +8203,10 @@
         <v>1146</v>
       </c>
       <c r="E247">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>251</v>
       </c>
@@ -8204,10 +8220,10 @@
         <v>1147</v>
       </c>
       <c r="E248">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>252</v>
       </c>
@@ -8221,10 +8237,10 @@
         <v>1148</v>
       </c>
       <c r="E249">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>253</v>
       </c>
@@ -8238,10 +8254,10 @@
         <v>1149</v>
       </c>
       <c r="E250">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>254</v>
       </c>
@@ -8255,10 +8271,10 @@
         <v>1150</v>
       </c>
       <c r="E251">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>255</v>
       </c>
@@ -8272,10 +8288,10 @@
         <v>1151</v>
       </c>
       <c r="E252">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>256</v>
       </c>
@@ -8289,10 +8305,10 @@
         <v>1152</v>
       </c>
       <c r="E253">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>257</v>
       </c>
@@ -8306,10 +8322,10 @@
         <v>1153</v>
       </c>
       <c r="E254">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>258</v>
       </c>
@@ -8323,10 +8339,10 @@
         <v>1154</v>
       </c>
       <c r="E255">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>259</v>
       </c>
@@ -8340,10 +8356,10 @@
         <v>1155</v>
       </c>
       <c r="E256">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>260</v>
       </c>
@@ -8357,645 +8373,645 @@
         <v>1156</v>
       </c>
       <c r="E257">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="273" spans="1:1">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="274" spans="1:1">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="275" spans="1:1">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="276" spans="1:1">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="277" spans="1:1">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="278" spans="1:1">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="279" spans="1:1">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="280" spans="1:1">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="281" spans="1:1">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="282" spans="1:1">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="283" spans="1:1">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="284" spans="1:1">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="285" spans="1:1">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="286" spans="1:1">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="287" spans="1:1">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="288" spans="1:1">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="289" spans="1:1">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="290" spans="1:1">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="291" spans="1:1">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="292" spans="1:1">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="293" spans="1:1">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="294" spans="1:1">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="295" spans="1:1">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="296" spans="1:1">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="297" spans="1:1">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="298" spans="1:1">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="299" spans="1:1">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="300" spans="1:1">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="301" spans="1:1">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="302" spans="1:1">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="303" spans="1:1">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="304" spans="1:1">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="305" spans="1:1">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="306" spans="1:1">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="307" spans="1:1">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="308" spans="1:1">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="309" spans="1:1">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="310" spans="1:1">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="311" spans="1:1">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="312" spans="1:1">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="313" spans="1:1">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="314" spans="1:1">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="315" spans="1:1">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="316" spans="1:1">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="317" spans="1:1">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="318" spans="1:1">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="319" spans="1:1">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="320" spans="1:1">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="321" spans="1:1">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="329" spans="1:1">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="330" spans="1:1">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="331" spans="1:1">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="332" spans="1:1">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="333" spans="1:1">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="334" spans="1:1">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="335" spans="1:1">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="336" spans="1:1">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="337" spans="1:1">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="338" spans="1:1">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="339" spans="1:1">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="340" spans="1:1">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="341" spans="1:1">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="342" spans="1:1">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="343" spans="1:1">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="344" spans="1:1">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="345" spans="1:1">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="346" spans="1:1">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="347" spans="1:1">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="348" spans="1:1">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="349" spans="1:1">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="350" spans="1:1">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="351" spans="1:1">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="352" spans="1:1">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="353" spans="1:1">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="354" spans="1:1">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="355" spans="1:1">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="356" spans="1:1">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="357" spans="1:1">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="358" spans="1:1">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="359" spans="1:1">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="360" spans="1:1">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="361" spans="1:1">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="362" spans="1:1">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="363" spans="1:1">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="364" spans="1:1">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="365" spans="1:1">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="366" spans="1:1">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="367" spans="1:1">
+    <row r="367" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="368" spans="1:1">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="369" spans="1:1">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="370" spans="1:1">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="371" spans="1:1">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="372" spans="1:1">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="373" spans="1:1">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="374" spans="1:1">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="375" spans="1:1">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="376" spans="1:1">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="377" spans="1:1">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="378" spans="1:1">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="379" spans="1:1">
+    <row r="379" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="380" spans="1:1">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="381" spans="1:1">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="382" spans="1:1">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="383" spans="1:1">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="384" spans="1:1">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="385" spans="1:1">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>388</v>
       </c>
@@ -9006,14 +9022,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="24" width="42.7109375" customWidth="1"/>
+    <col min="1" max="24" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1181</v>
       </c>
@@ -9090,7 +9106,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="2" customFormat="1">
+    <row r="2" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1182</v>
       </c>
@@ -9167,7 +9183,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1183</v>
       </c>
@@ -9244,7 +9260,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="2" customFormat="1">
+    <row r="4" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1184</v>
       </c>
@@ -9321,7 +9337,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1185</v>
       </c>
@@ -9398,7 +9414,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="6" spans="1:25" s="2" customFormat="1">
+    <row r="6" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>1186</v>
       </c>
@@ -9475,7 +9491,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1187</v>
       </c>
@@ -9552,7 +9568,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="2" customFormat="1">
+    <row r="8" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>1188</v>
       </c>
@@ -9629,7 +9645,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>1189</v>
       </c>
@@ -9706,7 +9722,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:25" s="2" customFormat="1">
+    <row r="10" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>1190</v>
       </c>
@@ -9783,7 +9799,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1191</v>
       </c>
@@ -9860,7 +9876,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="2" customFormat="1">
+    <row r="12" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1192</v>
       </c>
@@ -9913,27 +9929,27 @@
         <v>644</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>1193</v>
       </c>
     </row>
-    <row r="14" spans="1:25" s="2" customFormat="1">
+    <row r="14" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>1194</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>1195</v>
       </c>
     </row>
-    <row r="16" spans="1:25" s="2" customFormat="1">
+    <row r="16" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>1196</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>1197</v>
       </c>
@@ -9944,14 +9960,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="24" width="5.7109375" customWidth="1"/>
+    <col min="1" max="24" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1181</v>
       </c>
@@ -10028,7 +10044,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1182</v>
       </c>
@@ -10105,7 +10121,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1183</v>
       </c>
@@ -10182,7 +10198,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1184</v>
       </c>
@@ -10259,7 +10275,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1185</v>
       </c>
@@ -10336,7 +10352,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>1186</v>
       </c>
@@ -10413,7 +10429,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1187</v>
       </c>
@@ -10490,7 +10506,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>1188</v>
       </c>
@@ -10567,7 +10583,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>1189</v>
       </c>
@@ -10644,7 +10660,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>1190</v>
       </c>
@@ -10721,7 +10737,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1191</v>
       </c>
@@ -10798,7 +10814,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1192</v>
       </c>
@@ -10851,27 +10867,27 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>1193</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>1194</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>1195</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>1196</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>1197</v>
       </c>
